--- a/table/Datas/#FlappyConfig.xlsx
+++ b/table/Datas/#FlappyConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>restitution</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>stun_time</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>invuln_time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,6 +581,16 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>restitution</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stun_time</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>invuln_time</t>
         </is>
       </c>
     </row>
@@ -588,6 +618,12 @@
       </c>
       <c r="I5" t="n">
         <v>0.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#FlappyConfig.xlsx
+++ b/table/Datas/#FlappyConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,26 @@
           <t>invuln_time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dash_mult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>dash_duration</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dash_charge_base</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dash_charge_dive</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +549,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +631,26 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>invuln_time</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>dash_mult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dash_duration</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>dash_charge_base</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>dash_charge_dive</t>
         </is>
       </c>
     </row>
@@ -624,6 +684,18 @@
       </c>
       <c r="K5" t="n">
         <v>0.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#FlappyConfig.xlsx
+++ b/table/Datas/#FlappyConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,26 @@
           <t>dash_charge_dive</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>chaser_start_x</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>chaser_initial_speed</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>chaser_acceleration</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>chaser_max_speed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +589,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -651,6 +691,26 @@
       <c r="O4" t="inlineStr">
         <is>
           <t>dash_charge_dive</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>chaser_start_x</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>chaser_initial_speed</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>chaser_acceleration</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>chaser_max_speed</t>
         </is>
       </c>
     </row>
@@ -696,6 +756,18 @@
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#FlappyConfig.xlsx
+++ b/table/Datas/#FlappyConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
           <t>chaser_max_speed</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>finish_brake</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -609,6 +614,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -711,6 +721,11 @@
       <c r="S4" t="inlineStr">
         <is>
           <t>chaser_max_speed</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>finish_brake</t>
         </is>
       </c>
     </row>
@@ -768,6 +783,9 @@
       </c>
       <c r="S5" t="n">
         <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
